--- a/المستهدف.xlsx
+++ b/المستهدف.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7aa1d8f405ba1d72/NDEDC_Production/Sources/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64FA1307-AB7E-48F8-8275-F82008AE0953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{69269F31-B93F-4A4D-ADD3-A805192EAECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6434ABCD-C420-4876-BE0A-271DC2C7D2E0}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,9 +34,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t>القطاعات</t>
+  </si>
+  <si>
+    <t>A3</t>
+  </si>
+  <si>
+    <t>A2</t>
+  </si>
+  <si>
+    <t>A1</t>
   </si>
   <si>
     <t xml:space="preserve">هندسة مدينة شربين                       </t>
@@ -401,32 +410,6 @@
     <dxf>
       <font>
         <b/>
-        <sz val="10"/>
-        <color rgb="FF000000"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="1" formatCode="0"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
         <i val="0"/>
         <strike val="0"/>
         <condense val="0"/>
@@ -447,6 +430,32 @@
           <bgColor rgb="FFFFFF00"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="1" formatCode="0"/>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
@@ -587,8 +596,8 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2839315E-6770-4451-9533-495B6E1685CE}" name="Table13" displayName="Table13" ref="A1:B60" totalsRowCount="1" headerRowDxfId="9" dataDxfId="7" totalsRowDxfId="5" headerRowBorderDxfId="8" tableBorderDxfId="6" totalsRowBorderDxfId="4">
   <autoFilter ref="A1:B59" xr:uid="{2839315E-6770-4451-9533-495B6E1685CE}"/>
   <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{05FE433A-4BB6-4577-97BE-C875A73AD801}" name="القطاعات" totalsRowLabel="كفر الشيخ" dataDxfId="3" totalsRowDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{60CAE18C-23CF-4716-A464-02978E7BE3E4}" name="A4+A5" totalsRowFunction="custom" dataDxfId="1" totalsRowDxfId="0">
+    <tableColumn id="1" xr3:uid="{05FE433A-4BB6-4577-97BE-C875A73AD801}" name="القطاعات" totalsRowLabel="كفر الشيخ" dataDxfId="3" totalsRowDxfId="1"/>
+    <tableColumn id="2" xr3:uid="{60CAE18C-23CF-4716-A464-02978E7BE3E4}" name="A4+A5" totalsRowFunction="custom" dataDxfId="2" totalsRowDxfId="0">
       <totalsRowFormula>SUBTOTAL(109,B43:B59)</totalsRowFormula>
     </tableColumn>
   </tableColumns>
@@ -859,505 +868,1069 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B61"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29" style="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.1640625" style="2"/>
+    <col min="2" max="5" width="11.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.1640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B2" s="3">
         <v>193</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="B3" s="3">
         <v>324</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="3">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B4" s="3">
         <v>271</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="3">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B5" s="3">
         <v>240</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="3">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3">
         <v>421</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C6" s="3">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B7" s="3">
         <v>223</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B8" s="3">
         <v>364</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B9" s="3">
         <v>254</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9" s="3">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B10" s="3">
         <v>308</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C10" s="3">
+        <v>0</v>
+      </c>
+      <c r="D10" s="3">
+        <v>0</v>
+      </c>
+      <c r="E10" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B11" s="3">
         <v>230</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C11" s="3">
+        <v>0</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+      <c r="E11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B12" s="3">
         <v>260</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C12" s="3">
+        <v>0</v>
+      </c>
+      <c r="D12" s="3">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B13" s="3">
         <v>296</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C13" s="3">
+        <v>0</v>
+      </c>
+      <c r="D13" s="3">
+        <v>0</v>
+      </c>
+      <c r="E13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B14" s="3">
         <v>119</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C14" s="3">
+        <v>0</v>
+      </c>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B15" s="3">
         <v>297</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C15" s="3">
+        <v>0</v>
+      </c>
+      <c r="D15" s="3">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B16" s="6">
         <f>SUBTOTAL(109,B2:B15)</f>
         <v>3800</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C16" s="6">
+        <f>SUBTOTAL(109,C2:C15)</f>
+        <v>0</v>
+      </c>
+      <c r="D16" s="6">
+        <f>SUBTOTAL(109,D2:D15)</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="6">
+        <f>SUBTOTAL(109,E2:E15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B17" s="3">
         <v>310</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C17" s="3">
+        <v>0</v>
+      </c>
+      <c r="D17" s="3">
+        <v>0</v>
+      </c>
+      <c r="E17" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B18" s="3">
         <v>535</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="3">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3">
+        <v>0</v>
+      </c>
+      <c r="E18" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B19" s="3">
         <v>250</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="3">
+        <v>0</v>
+      </c>
+      <c r="D19" s="3">
+        <v>0</v>
+      </c>
+      <c r="E19" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B20" s="3">
         <v>95</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C20" s="3">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B21" s="3">
         <v>829</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C21" s="3">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B22" s="3">
         <v>232</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C22" s="3">
+        <v>0</v>
+      </c>
+      <c r="D22" s="3">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B23" s="3">
         <v>162</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C23" s="3">
+        <v>0</v>
+      </c>
+      <c r="D23" s="3">
+        <v>0</v>
+      </c>
+      <c r="E23" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B24" s="3">
         <v>434</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C24" s="3">
+        <v>0</v>
+      </c>
+      <c r="D24" s="3">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B25" s="3">
         <v>369</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C25" s="3">
+        <v>0</v>
+      </c>
+      <c r="D25" s="3">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B26" s="3">
         <v>281</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C26" s="3">
+        <v>0</v>
+      </c>
+      <c r="D26" s="3">
+        <v>0</v>
+      </c>
+      <c r="E26" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B27" s="3">
         <v>299</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
+      <c r="E27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B28" s="6">
         <f>SUBTOTAL(109,B17:B27)</f>
         <v>3796</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C28" s="6">
+        <f>SUBTOTAL(109,C17:C27)</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="6">
+        <f>SUBTOTAL(109,D17:D27)</f>
+        <v>0</v>
+      </c>
+      <c r="E28" s="6">
+        <f>SUBTOTAL(109,E17:E27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B29" s="3">
         <v>707</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C29" s="3">
+        <v>0</v>
+      </c>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B30" s="3">
         <v>880</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C30" s="3">
+        <v>0</v>
+      </c>
+      <c r="D30" s="3">
+        <v>0</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B31" s="3">
         <v>637</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C31" s="3">
+        <v>0</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0</v>
+      </c>
+      <c r="E31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B32" s="3">
         <v>371</v>
       </c>
-    </row>
-    <row r="33" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C32" s="3">
+        <v>0</v>
+      </c>
+      <c r="D32" s="3">
+        <v>0</v>
+      </c>
+      <c r="E32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B33" s="3">
         <v>497</v>
       </c>
-    </row>
-    <row r="34" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C33" s="3">
+        <v>0</v>
+      </c>
+      <c r="D33" s="3">
+        <v>0</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B34" s="3">
         <v>387</v>
       </c>
-    </row>
-    <row r="35" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C34" s="3">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B35" s="3">
         <v>760</v>
       </c>
-    </row>
-    <row r="36" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C35" s="3">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B36" s="3">
         <v>139</v>
       </c>
-    </row>
-    <row r="37" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C36" s="3">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B37" s="3">
         <v>571</v>
       </c>
-    </row>
-    <row r="38" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C37" s="3">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B38" s="3">
         <v>275</v>
       </c>
-    </row>
-    <row r="39" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C38" s="3">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B39" s="3">
         <v>339</v>
       </c>
-    </row>
-    <row r="40" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C39" s="3">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B40" s="3">
         <v>475</v>
       </c>
-    </row>
-    <row r="41" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C40" s="3">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B41" s="3">
         <v>345</v>
       </c>
-    </row>
-    <row r="42" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C41" s="3">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B42" s="6">
         <f>SUBTOTAL(109,B29:B41)</f>
         <v>6383</v>
       </c>
-    </row>
-    <row r="43" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C42" s="6">
+        <f>SUBTOTAL(109,C29:C41)</f>
+        <v>0</v>
+      </c>
+      <c r="D42" s="6">
+        <f>SUBTOTAL(109,D29:D41)</f>
+        <v>0</v>
+      </c>
+      <c r="E42" s="6">
+        <f>SUBTOTAL(109,E29:E41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B43" s="3">
         <v>446</v>
       </c>
-    </row>
-    <row r="44" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C43" s="3">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B44" s="3">
         <v>357</v>
       </c>
-    </row>
-    <row r="45" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C44" s="3">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B45" s="3">
         <v>332</v>
       </c>
-    </row>
-    <row r="46" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C45" s="3">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B46" s="3">
         <v>313</v>
       </c>
-    </row>
-    <row r="47" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C46" s="3">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B47" s="3">
         <v>389</v>
       </c>
-    </row>
-    <row r="48" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C47" s="3">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="4" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B48" s="3">
         <v>353</v>
       </c>
-    </row>
-    <row r="49" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C48" s="3">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B49" s="3">
         <v>435</v>
       </c>
-    </row>
-    <row r="50" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C49" s="3">
+        <v>0</v>
+      </c>
+      <c r="D49" s="3">
+        <v>0</v>
+      </c>
+      <c r="E49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B50" s="3">
         <v>201</v>
       </c>
-    </row>
-    <row r="51" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C50" s="3">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B51" s="3">
         <v>385</v>
       </c>
-    </row>
-    <row r="52" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C51" s="3">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B52" s="3">
         <v>225</v>
       </c>
-    </row>
-    <row r="53" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C52" s="3">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B53" s="3">
         <v>332</v>
       </c>
-    </row>
-    <row r="54" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C53" s="3">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B54" s="3">
         <v>586</v>
       </c>
-    </row>
-    <row r="55" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C54" s="3">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B55" s="3">
         <v>243</v>
       </c>
-    </row>
-    <row r="56" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C55" s="3">
+        <v>0</v>
+      </c>
+      <c r="D55" s="3">
+        <v>0</v>
+      </c>
+      <c r="E55" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B56" s="3">
         <v>333</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C56" s="3">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B57" s="3">
         <v>502</v>
       </c>
-    </row>
-    <row r="58" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C57" s="3">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B58" s="3">
         <v>365</v>
       </c>
-    </row>
-    <row r="59" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C58" s="3">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B59" s="3">
         <v>155</v>
       </c>
-    </row>
-    <row r="60" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C59" s="3">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B60" s="6">
         <f>SUBTOTAL(109,B43:B59)</f>
         <v>5952</v>
       </c>
-    </row>
-    <row r="61" spans="1:2" ht="16" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C60" s="6">
+        <f>SUBTOTAL(109,C43:C59)</f>
+        <v>0</v>
+      </c>
+      <c r="D60" s="6">
+        <f>SUBTOTAL(109,D43:D59)</f>
+        <v>0</v>
+      </c>
+      <c r="E60" s="6">
+        <f>SUBTOTAL(109,E43:E59)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="16" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B61" s="8">
         <f>B16+B28+B42+Table13[[#Totals],[A4+A5]]</f>
         <v>19931</v>
+      </c>
+      <c r="C61" s="8">
+        <f>C16+C28+C42+Table13[[#Totals],[A4+A5]]</f>
+        <v>5952</v>
+      </c>
+      <c r="D61" s="8">
+        <f>D16+D28+D42+Table13[[#Totals],[A4+A5]]</f>
+        <v>5952</v>
+      </c>
+      <c r="E61" s="8">
+        <f>E16+E28+E42+Table13[[#Totals],[A4+A5]]</f>
+        <v>5952</v>
       </c>
     </row>
   </sheetData>
